--- a/kaufpunkte_aktuell.xlsx
+++ b/kaufpunkte_aktuell.xlsx
@@ -14721,7 +14721,7 @@
       </c>
       <c r="K119" s="2" t="inlineStr">
         <is>
-          <t>+22%</t>
+          <t>+23%</t>
         </is>
       </c>
       <c r="L119" s="2" t="inlineStr">
@@ -16862,12 +16862,12 @@
       </c>
       <c r="J137" s="3" t="inlineStr">
         <is>
-          <t>✓ +70%</t>
+          <t>✗ -23%</t>
         </is>
       </c>
       <c r="K137" s="3" t="inlineStr">
         <is>
-          <t>+529%</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="L137" s="3" t="inlineStr">
